--- a/diseases/d035/2010-2014.xlsx
+++ b/diseases/d035/2010-2014.xlsx
@@ -1357,9 +1357,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -2245,9 +2242,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3127,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4012,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -4909,9 +4897,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -5797,9 +5782,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -6685,9 +6667,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -7573,9 +7552,6 @@
       <c r="O48" t="n">
         <v>5</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01025234454459675</v>
       </c>
@@ -8461,9 +8437,6 @@
       <c r="O54" t="n">
         <v>12</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.0246056269070322</v>
       </c>
@@ -9349,9 +9322,6 @@
       <c r="O60" t="n">
         <v>17</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.03485797145162895</v>
       </c>
@@ -10237,9 +10207,6 @@
       <c r="O66" t="n">
         <v>17</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.03485797145162895</v>
       </c>
@@ -11125,9 +11092,6 @@
       <c r="O72" t="n">
         <v>6</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.0123028134535161</v>
       </c>
@@ -12013,9 +11977,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12901,9 +12862,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -13789,9 +13747,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14677,9 +14632,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15565,9 +15517,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -16453,9 +16402,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17341,9 +17287,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18229,9 +18172,6 @@
       <c r="O120" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -19117,9 +19057,6 @@
       <c r="O126" t="n">
         <v>14</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.02849719425276321</v>
       </c>
@@ -20005,9 +19942,6 @@
       <c r="O132" t="n">
         <v>12</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.02442616650236847</v>
       </c>
@@ -20893,9 +20827,6 @@
       <c r="O138" t="n">
         <v>15</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.03053270812796058</v>
       </c>
@@ -21781,9 +21712,6 @@
       <c r="O144" t="n">
         <v>4</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -22669,9 +22597,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -23557,9 +23482,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24297,9 +24219,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25185,9 +25104,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26073,9 +25989,6 @@
       <c r="O173" t="n">
         <v>2</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -26961,9 +26874,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -27849,9 +27759,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -28737,9 +28644,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -29625,9 +29529,6 @@
       <c r="O197" t="n">
         <v>5</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.01008073062393603</v>
       </c>
@@ -30957,9 +30858,6 @@
       <c r="O206" t="n">
         <v>10</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.02016146124787207</v>
       </c>
@@ -32437,9 +32335,6 @@
       <c r="O216" t="n">
         <v>8</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.01612916899829766</v>
       </c>
@@ -34065,9 +33960,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35545,9 +35437,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -37173,9 +37062,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38653,9 +38539,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -40133,9 +40016,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -41613,9 +41493,6 @@
       <c r="O278" t="n">
         <v>2</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -43241,9 +43118,6 @@
       <c r="O289" t="n">
         <v>2</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -44721,9 +44595,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -46201,9 +46072,6 @@
       <c r="O309" t="n">
         <v>5</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.009985787328752859</v>
       </c>
@@ -47829,9 +47697,6 @@
       <c r="O320" t="n">
         <v>10</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.01997157465750572</v>
       </c>
@@ -49309,9 +49174,6 @@
       <c r="O330" t="n">
         <v>19</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.03794599184926086</v>
       </c>
@@ -50937,9 +50799,6 @@
       <c r="O341" t="n">
         <v>11</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.02196873212325629</v>
       </c>
@@ -52417,9 +52276,6 @@
       <c r="O351" t="n">
         <v>1</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -53897,9 +53753,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -54293,9 +54146,6 @@
       <c r="O363" t="n">
         <v>1</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -55921,9 +55771,6 @@
       <c r="O374" t="n">
         <v>1</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -57401,9 +57248,6 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
@@ -58881,9 +58725,6 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
@@ -60361,9 +60202,6 @@
       <c r="O404" t="n">
         <v>1</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -61989,9 +61827,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -63469,9 +63304,6 @@
       <c r="O425" t="n">
         <v>1</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -65097,9 +64929,6 @@
       <c r="O436" t="n">
         <v>4</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0.007914671060680983</v>
       </c>
@@ -66577,9 +66406,6 @@
       <c r="O446" t="n">
         <v>16</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0.03165868424272393</v>
       </c>
@@ -68057,9 +67883,6 @@
       <c r="O456" t="n">
         <v>17</v>
       </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
       <c r="R456" t="n">
         <v>0.03363735200789417</v>
       </c>
@@ -69685,9 +69508,6 @@
       <c r="O467" t="n">
         <v>13</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0.02572268094721319</v>
       </c>
@@ -71164,9 +70984,6 @@
       </c>
       <c r="O477" t="n">
         <v>4</v>
-      </c>
-      <c r="Q477" t="n">
-        <v>0</v>
       </c>
       <c r="R477" t="n">
         <v>0.007914671060680983</v>
